--- a/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_by_Sample_name.xlsx
@@ -871,10 +871,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>37.5918082071325</v>
+        <v>37.6083286086558</v>
       </c>
       <c r="H2" t="n">
-        <v>5.59724283853563</v>
+        <v>5.60163716781323</v>
       </c>
     </row>
     <row r="3">
@@ -897,10 +897,10 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>19.2288487135942</v>
+        <v>19.218471533848</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24433712249579</v>
+        <v>2.2429594916445</v>
       </c>
     </row>
     <row r="4">
@@ -923,10 +923,10 @@
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>8.83085837103093</v>
+        <v>8.83030019633991</v>
       </c>
       <c r="H4" t="n">
-        <v>1.18874316365223</v>
+        <v>1.18860523810051</v>
       </c>
     </row>
     <row r="5">
@@ -949,10 +949,10 @@
         <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>8.09463516172468</v>
+        <v>8.09618084032267</v>
       </c>
       <c r="H5" t="n">
-        <v>1.77500895016411</v>
+        <v>1.77463760386218</v>
       </c>
     </row>
     <row r="6">
@@ -975,10 +975,10 @@
         <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>6.10421054572848</v>
+        <v>6.10113835323846</v>
       </c>
       <c r="H6" t="n">
-        <v>0.294523157391094</v>
+        <v>0.294258916288561</v>
       </c>
     </row>
     <row r="7">
@@ -1001,10 +1001,10 @@
         <v>28</v>
       </c>
       <c r="G7" t="n">
-        <v>4.26967222633716</v>
+        <v>4.26749999551657</v>
       </c>
       <c r="H7" t="n">
-        <v>0.136065425139798</v>
+        <v>0.136006692264525</v>
       </c>
     </row>
     <row r="8">
@@ -1027,10 +1027,10 @@
         <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>2.37864315458891</v>
+        <v>2.37709253061693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.358294868454593</v>
+        <v>0.357981212416598</v>
       </c>
     </row>
     <row r="9">
@@ -1053,10 +1053,10 @@
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.01852135990976</v>
+        <v>2.01755200520453</v>
       </c>
       <c r="H9" t="n">
-        <v>0.47286582764833</v>
+        <v>0.472637173749157</v>
       </c>
     </row>
     <row r="10">
@@ -1079,10 +1079,10 @@
         <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>1.77795158750644</v>
+        <v>1.77831365140166</v>
       </c>
       <c r="H10" t="n">
-        <v>0.123717695718346</v>
+        <v>0.123792722581263</v>
       </c>
     </row>
     <row r="11">
@@ -1105,10 +1105,10 @@
         <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75810325427876</v>
+        <v>1.75771279197965</v>
       </c>
       <c r="H11" t="n">
-        <v>0.105375468444451</v>
+        <v>0.105305005221165</v>
       </c>
     </row>
     <row r="12">
@@ -1131,10 +1131,10 @@
         <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>1.60491681905068</v>
+        <v>1.60475341957924</v>
       </c>
       <c r="H12" t="n">
-        <v>0.203347398935847</v>
+        <v>0.203320697582051</v>
       </c>
     </row>
     <row r="13">
@@ -1157,10 +1157,10 @@
         <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>1.60022858826323</v>
+        <v>1.59952430806309</v>
       </c>
       <c r="H13" t="n">
-        <v>1.11371431019001</v>
+        <v>1.11322173383588</v>
       </c>
     </row>
     <row r="14">
@@ -1183,10 +1183,10 @@
         <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>1.55086169293292</v>
+        <v>1.55006532100056</v>
       </c>
       <c r="H14" t="n">
-        <v>0.195944034605326</v>
+        <v>0.195757121469496</v>
       </c>
     </row>
     <row r="15">
@@ -1209,10 +1209,10 @@
         <v>46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.37355874984232</v>
+        <v>1.37632070583837</v>
       </c>
       <c r="H15" t="n">
-        <v>0.608027825036764</v>
+        <v>0.609441380320974</v>
       </c>
     </row>
     <row r="16">
@@ -1235,10 +1235,10 @@
         <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>0.477247905242917</v>
+        <v>0.477051715520837</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0450023147999319</v>
+        <v>0.0449831141801297</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         <v>54</v>
       </c>
       <c r="G17" t="n">
-        <v>0.476758293076138</v>
+        <v>0.476429470271012</v>
       </c>
       <c r="H17"/>
     </row>
@@ -1285,10 +1285,10 @@
         <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>0.149104779513924</v>
+        <v>0.149030260473569</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0316941592935839</v>
+        <v>0.0316346864463296</v>
       </c>
     </row>
     <row r="19">
@@ -1311,7 +1311,7 @@
         <v>59</v>
       </c>
       <c r="G19" t="n">
-        <v>0.115689526293467</v>
+        <v>0.115783032995387</v>
       </c>
       <c r="H19"/>
     </row>
@@ -1335,10 +1335,10 @@
         <v>64</v>
       </c>
       <c r="G20" t="n">
-        <v>0.10336839725838</v>
+        <v>0.10349339817975</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0254780013641728</v>
+        <v>0.0254968433941032</v>
       </c>
     </row>
     <row r="21">
@@ -1361,10 +1361,10 @@
         <v>69</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0959531044181956</v>
+        <v>0.0959849204084664</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0184027177895018</v>
+        <v>0.0184107366986344</v>
       </c>
     </row>
     <row r="22">
@@ -1387,10 +1387,10 @@
         <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0836277009911762</v>
+        <v>0.0836599616266827</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0227641652334727</v>
+        <v>0.0227635062895201</v>
       </c>
     </row>
     <row r="23">
@@ -1413,10 +1413,10 @@
         <v>73</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0314614675263603</v>
+        <v>0.0314612322227579</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0127804314420856</v>
+        <v>0.0127689933560534</v>
       </c>
     </row>
     <row r="24">
@@ -1439,7 +1439,7 @@
         <v>76</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0313025378626997</v>
+        <v>0.0312869414447345</v>
       </c>
       <c r="H24"/>
     </row>
@@ -1463,7 +1463,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0302541460960583</v>
+        <v>0.03022256435489</v>
       </c>
       <c r="H25"/>
     </row>
@@ -1487,7 +1487,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0294676579805349</v>
+        <v>0.0294473779769107</v>
       </c>
       <c r="H26"/>
     </row>
@@ -1511,7 +1511,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0291536844640611</v>
+        <v>0.0291678916513498</v>
       </c>
       <c r="H27"/>
     </row>
@@ -1535,10 +1535,10 @@
         <v>81</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0171410888102613</v>
+        <v>0.0171340644586921</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00245607478419209</v>
+        <v>0.00245636789191226</v>
       </c>
     </row>
     <row r="29">
@@ -1561,10 +1561,10 @@
         <v>83</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0149382226408432</v>
+        <v>0.0149226289076914</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00136422470911702</v>
+        <v>0.00136280062028233</v>
       </c>
     </row>
     <row r="30">
@@ -1587,10 +1587,10 @@
         <v>85</v>
       </c>
       <c r="G30" t="n">
-        <v>0.013929077563761</v>
+        <v>0.013918419012933</v>
       </c>
       <c r="H30" t="n">
-        <v>0.00388577358234299</v>
+        <v>0.00388446211042003</v>
       </c>
     </row>
     <row r="31">
@@ -1613,7 +1613,7 @@
         <v>87</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0137048662778633</v>
+        <v>0.0136905600225104</v>
       </c>
       <c r="H31"/>
     </row>
@@ -1637,7 +1637,7 @@
         <v>90</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0130089175550854</v>
+        <v>0.0129953377876777</v>
       </c>
       <c r="H32"/>
     </row>
@@ -1661,7 +1661,7 @@
         <v>91</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0119830634913592</v>
+        <v>0.0119938451210844</v>
       </c>
       <c r="H33"/>
     </row>
@@ -1685,7 +1685,7 @@
         <v>92</v>
       </c>
       <c r="G34" t="n">
-        <v>0.011905735855495</v>
+        <v>0.011911940100677</v>
       </c>
       <c r="H34"/>
     </row>
@@ -1709,7 +1709,7 @@
         <v>95</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0115462983521061</v>
+        <v>0.0115447261229262</v>
       </c>
       <c r="H35"/>
     </row>
@@ -1733,10 +1733,10 @@
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0107555358446505</v>
+        <v>0.0107466373932689</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00383713958969168</v>
+        <v>0.00383148718197804</v>
       </c>
     </row>
     <row r="37">
@@ -1759,7 +1759,7 @@
         <v>97</v>
       </c>
       <c r="G37" t="n">
-        <v>0.00982099833583932</v>
+        <v>0.00983170785250912</v>
       </c>
       <c r="H37"/>
     </row>
@@ -1783,7 +1783,7 @@
         <v>99</v>
       </c>
       <c r="G38" t="n">
-        <v>0.00838480264662265</v>
+        <v>0.00838381341592277</v>
       </c>
       <c r="H38"/>
     </row>
@@ -1807,7 +1807,7 @@
         <v>100</v>
       </c>
       <c r="G39" t="n">
-        <v>0.00632532289747537</v>
+        <v>0.00631872001038943</v>
       </c>
       <c r="H39"/>
     </row>
@@ -1831,7 +1831,7 @@
         <v>101</v>
       </c>
       <c r="G40" t="n">
-        <v>0.00598920025917114</v>
+        <v>0.00598838270059453</v>
       </c>
       <c r="H40"/>
     </row>
@@ -1855,7 +1855,7 @@
         <v>102</v>
       </c>
       <c r="G41" t="n">
-        <v>0.00520348930581722</v>
+        <v>0.00519805747998064</v>
       </c>
       <c r="H41"/>
     </row>
@@ -1879,7 +1879,7 @@
         <v>103</v>
       </c>
       <c r="G42" t="n">
-        <v>0.00421688193165025</v>
+        <v>0.00421248000692629</v>
       </c>
       <c r="H42"/>
     </row>
@@ -1903,7 +1903,7 @@
         <v>104</v>
       </c>
       <c r="G43" t="n">
-        <v>0.00316266144873768</v>
+        <v>0.00315936000519471</v>
       </c>
       <c r="H43"/>
     </row>
@@ -1927,7 +1927,7 @@
         <v>105</v>
       </c>
       <c r="G44" t="n">
-        <v>0.00177620413836834</v>
+        <v>0.00177629086912041</v>
       </c>
       <c r="H44"/>
     </row>
@@ -1988,10 +1988,10 @@
         <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>59.7972040101877</v>
+        <v>60.0117510250063</v>
       </c>
       <c r="H2" t="n">
-        <v>18.976589310687</v>
+        <v>19.0438950283452</v>
       </c>
     </row>
     <row r="3">
@@ -2014,10 +2014,10 @@
         <v>96</v>
       </c>
       <c r="G3" t="n">
-        <v>5.08412417040453</v>
+        <v>5.06950231319807</v>
       </c>
       <c r="H3" t="n">
-        <v>0.378320464919258</v>
+        <v>0.377113265596081</v>
       </c>
     </row>
     <row r="4">
@@ -2040,10 +2040,10 @@
         <v>91</v>
       </c>
       <c r="G4" t="n">
-        <v>4.16402403656973</v>
+        <v>4.15037371346815</v>
       </c>
       <c r="H4" t="n">
-        <v>0.299884651886955</v>
+        <v>0.298869369114413</v>
       </c>
     </row>
     <row r="5">
@@ -2066,10 +2066,10 @@
         <v>107</v>
       </c>
       <c r="G5" t="n">
-        <v>3.93158489246636</v>
+        <v>3.91628565898143</v>
       </c>
       <c r="H5" t="n">
-        <v>0.872327316513051</v>
+        <v>0.86893051462819</v>
       </c>
     </row>
     <row r="6">
@@ -2092,10 +2092,10 @@
         <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>3.81327766135551</v>
+        <v>3.80029069964622</v>
       </c>
       <c r="H6" t="n">
-        <v>0.37093051720837</v>
+        <v>0.36973218053426</v>
       </c>
     </row>
     <row r="7">
@@ -2118,10 +2118,10 @@
         <v>109</v>
       </c>
       <c r="G7" t="n">
-        <v>2.94114609019628</v>
+        <v>2.9321907332996</v>
       </c>
       <c r="H7" t="n">
-        <v>0.475906441031753</v>
+        <v>0.474481791006024</v>
       </c>
     </row>
     <row r="8">
@@ -2144,10 +2144,10 @@
         <v>101</v>
       </c>
       <c r="G8" t="n">
-        <v>2.40917727168055</v>
+        <v>2.40137568481719</v>
       </c>
       <c r="H8" t="n">
-        <v>0.237419943165833</v>
+        <v>0.236511107257356</v>
       </c>
     </row>
     <row r="9">
@@ -2170,10 +2170,10 @@
         <v>58</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09049528070063</v>
+        <v>2.08450445689778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.145951914845706</v>
+        <v>0.145559562754144</v>
       </c>
     </row>
     <row r="10">
@@ -2196,10 +2196,10 @@
         <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>1.73075091445215</v>
+        <v>1.72381281041984</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0592720139891462</v>
+        <v>0.0588899026502082</v>
       </c>
     </row>
     <row r="11">
@@ -2222,10 +2222,10 @@
         <v>114</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5926287706612</v>
+        <v>1.58739391009556</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0727730115844399</v>
+        <v>0.0724926926103326</v>
       </c>
     </row>
     <row r="12">
@@ -2248,10 +2248,10 @@
         <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>1.43185255134799</v>
+        <v>1.42773642490983</v>
       </c>
       <c r="H12" t="n">
-        <v>0.140631554052836</v>
+        <v>0.140218801800912</v>
       </c>
     </row>
     <row r="13">
@@ -2274,10 +2274,10 @@
         <v>115</v>
       </c>
       <c r="G13" t="n">
-        <v>1.26992267145062</v>
+        <v>1.26518242062795</v>
       </c>
       <c r="H13" t="n">
-        <v>0.892188850299104</v>
+        <v>0.888839406762089</v>
       </c>
     </row>
     <row r="14">
@@ -2285,25 +2285,25 @@
         <v>106</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="G14" t="n">
-        <v>1.08440498494746</v>
+        <v>1.05273298931228</v>
       </c>
       <c r="H14" t="n">
-        <v>0.346796377127552</v>
+        <v>0.284072970788701</v>
       </c>
     </row>
     <row r="15">
@@ -2311,25 +2311,25 @@
         <v>106</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>1.05615453923259</v>
+        <v>1.0256963259798</v>
       </c>
       <c r="H15" t="n">
-        <v>0.285038618882002</v>
+        <v>0.326196478513884</v>
       </c>
     </row>
     <row r="16">
@@ -2352,10 +2352,10 @@
         <v>118</v>
       </c>
       <c r="G16" t="n">
-        <v>1.01029569541414</v>
+        <v>1.00732325949899</v>
       </c>
       <c r="H16" t="n">
-        <v>0.155699893922854</v>
+        <v>0.15499034216812</v>
       </c>
     </row>
     <row r="17">
@@ -2363,25 +2363,25 @@
         <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>0.918635764339107</v>
+        <v>0.889608254811833</v>
       </c>
       <c r="H17" t="n">
-        <v>0.160565559093251</v>
+        <v>0.0858885730237929</v>
       </c>
     </row>
     <row r="18">
@@ -2389,25 +2389,25 @@
         <v>106</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>0.892286873206269</v>
+        <v>0.888043173298091</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0861615657028079</v>
+        <v>0.15131718509958</v>
       </c>
     </row>
     <row r="19">
@@ -2430,10 +2430,10 @@
         <v>119</v>
       </c>
       <c r="G19" t="n">
-        <v>0.725763207508523</v>
+        <v>0.723314350063458</v>
       </c>
       <c r="H19" t="n">
-        <v>0.133108652464746</v>
+        <v>0.132616467895333</v>
       </c>
     </row>
     <row r="20">
@@ -2456,10 +2456,10 @@
         <v>120</v>
       </c>
       <c r="G20" t="n">
-        <v>0.510125206600034</v>
+        <v>0.508159708101382</v>
       </c>
       <c r="H20" t="n">
-        <v>0.153437827279288</v>
+        <v>0.152848319160961</v>
       </c>
     </row>
     <row r="21">
@@ -2482,10 +2482,10 @@
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>0.402296245812782</v>
+        <v>0.401484811843114</v>
       </c>
       <c r="H21" t="n">
-        <v>0.274871069987508</v>
+        <v>0.274321679413749</v>
       </c>
     </row>
     <row r="22">
@@ -2508,10 +2508,10 @@
         <v>35</v>
       </c>
       <c r="G22" t="n">
-        <v>0.312482786672822</v>
+        <v>0.311671152729996</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0188291509493229</v>
+        <v>0.0187817710109833</v>
       </c>
     </row>
     <row r="23">
@@ -2534,10 +2534,10 @@
         <v>121</v>
       </c>
       <c r="G23" t="n">
-        <v>0.267598050052906</v>
+        <v>0.266858246702524</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0477230125985776</v>
+        <v>0.0475778262628635</v>
       </c>
     </row>
     <row r="24">
@@ -2560,10 +2560,10 @@
         <v>102</v>
       </c>
       <c r="G24" t="n">
-        <v>0.251524746494149</v>
+        <v>0.250918139107696</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0617643265782247</v>
+        <v>0.0615902524901897</v>
       </c>
     </row>
     <row r="25">
@@ -2586,7 +2586,7 @@
         <v>73</v>
       </c>
       <c r="G25" t="n">
-        <v>0.23728962573427</v>
+        <v>0.237184269250681</v>
       </c>
       <c r="H25"/>
     </row>
@@ -2610,10 +2610,10 @@
         <v>122</v>
       </c>
       <c r="G26" t="n">
-        <v>0.222535631787799</v>
+        <v>0.221710650735825</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0496963452051179</v>
+        <v>0.0495197979168024</v>
       </c>
     </row>
     <row r="27">
@@ -2636,10 +2636,10 @@
         <v>123</v>
       </c>
       <c r="G27" t="n">
-        <v>0.216347925314775</v>
+        <v>0.215870883757239</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0668673101665294</v>
+        <v>0.0667053324383637</v>
       </c>
     </row>
     <row r="28">
@@ -2662,10 +2662,10 @@
         <v>124</v>
       </c>
       <c r="G28" t="n">
-        <v>0.209293335630761</v>
+        <v>0.208697016587328</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0247828240409539</v>
+        <v>0.0248312916642687</v>
       </c>
     </row>
     <row r="29">
@@ -2688,10 +2688,10 @@
         <v>87</v>
       </c>
       <c r="G29" t="n">
-        <v>0.159158233406459</v>
+        <v>0.158629451887912</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0295571863286935</v>
+        <v>0.029447927436553</v>
       </c>
     </row>
     <row r="30">
@@ -2714,10 +2714,10 @@
         <v>34</v>
       </c>
       <c r="G30" t="n">
-        <v>0.154946550045472</v>
+        <v>0.154550068786171</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0127021282448725</v>
+        <v>0.0126700359958705</v>
       </c>
     </row>
     <row r="31">
@@ -2740,10 +2740,10 @@
         <v>125</v>
       </c>
       <c r="G31" t="n">
-        <v>0.14602048732206</v>
+        <v>0.145486681207573</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0753360802189084</v>
+        <v>0.0750377257412392</v>
       </c>
     </row>
     <row r="32">
@@ -2766,10 +2766,10 @@
         <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>0.132284452778502</v>
+        <v>0.13250593027904</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0278585800252594</v>
+        <v>0.0279680233633284</v>
       </c>
     </row>
     <row r="33">
@@ -2792,10 +2792,10 @@
         <v>126</v>
       </c>
       <c r="G33" t="n">
-        <v>0.123747444673224</v>
+        <v>0.123510971749274</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0119104254278716</v>
+        <v>0.0118918963869835</v>
       </c>
     </row>
     <row r="34">
@@ -2818,10 +2818,10 @@
         <v>127</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1219565901681</v>
+        <v>0.121582177859253</v>
       </c>
       <c r="H34" t="n">
-        <v>0.03803876552827</v>
+        <v>0.037898217014805</v>
       </c>
     </row>
     <row r="35">
@@ -2844,10 +2844,10 @@
         <v>50</v>
       </c>
       <c r="G35" t="n">
-        <v>0.108520301484974</v>
+        <v>0.105343591806292</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0146072490474575</v>
+        <v>0.0136460636697803</v>
       </c>
     </row>
     <row r="36">
@@ -2870,10 +2870,10 @@
         <v>128</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0890465803462761</v>
+        <v>0.0888390111238276</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0246015140262958</v>
+        <v>0.0245311096322552</v>
       </c>
     </row>
     <row r="37">
@@ -2896,10 +2896,10 @@
         <v>129</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0832630361105788</v>
+        <v>0.0830283997127392</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0148600428875005</v>
+        <v>0.0148023489396302</v>
       </c>
     </row>
     <row r="38">
@@ -2922,7 +2922,7 @@
         <v>130</v>
       </c>
       <c r="G38" t="n">
-        <v>0.058275435053976</v>
+        <v>0.0581071791544456</v>
       </c>
       <c r="H38"/>
     </row>
@@ -2946,7 +2946,7 @@
         <v>131</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0428169982267665</v>
+        <v>0.0426359569876034</v>
       </c>
       <c r="H39"/>
     </row>
@@ -2970,10 +2970,10 @@
         <v>30</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0300883611222613</v>
+        <v>0.0299835057369271</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00283580264993809</v>
+        <v>0.00282661171792033</v>
       </c>
     </row>
     <row r="41">
@@ -2996,10 +2996,10 @@
         <v>132</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0250942902611634</v>
+        <v>0.0250102848261307</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00339320513522455</v>
+        <v>0.00339138062886281</v>
       </c>
     </row>
     <row r="42">
@@ -3022,10 +3022,10 @@
         <v>133</v>
       </c>
       <c r="G42" t="n">
-        <v>0.020951460208884</v>
+        <v>0.0208668659802501</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0133694462915048</v>
+        <v>0.0133100927238196</v>
       </c>
     </row>
     <row r="43">
@@ -3048,7 +3048,7 @@
         <v>134</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0173061120239856</v>
+        <v>0.0172680837856723</v>
       </c>
       <c r="H43"/>
     </row>
@@ -3072,10 +3072,10 @@
         <v>138</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0151854301157901</v>
+        <v>0.015146783271896</v>
       </c>
       <c r="H44" t="n">
-        <v>0.00296997966832071</v>
+        <v>0.00296250525510009</v>
       </c>
     </row>
     <row r="45">
@@ -3098,10 +3098,10 @@
         <v>103</v>
       </c>
       <c r="G45" t="n">
-        <v>0.012865140460215</v>
+        <v>0.0128237901336455</v>
       </c>
       <c r="H45" t="n">
-        <v>0.00427865768425411</v>
+        <v>0.00425134095410153</v>
       </c>
     </row>
     <row r="46">
@@ -3124,7 +3124,7 @@
         <v>139</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0125653945997828</v>
+        <v>0.0125422192420528</v>
       </c>
       <c r="H46"/>
     </row>
@@ -3148,10 +3148,10 @@
         <v>140</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0124981456400159</v>
+        <v>0.0124453002779491</v>
       </c>
       <c r="H47" t="n">
-        <v>0.000238800886241983</v>
+        <v>0.000237791174908891</v>
       </c>
     </row>
     <row r="48">
@@ -3174,10 +3174,10 @@
         <v>42</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0105005975130238</v>
+        <v>0.010467780644986</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00117224346321637</v>
+        <v>0.00116856849201158</v>
       </c>
     </row>
     <row r="49">
@@ -3200,7 +3200,7 @@
         <v>141</v>
       </c>
       <c r="G49" t="n">
-        <v>0.00775421951793163</v>
+        <v>0.00773447947463692</v>
       </c>
       <c r="H49"/>
     </row>
@@ -3224,7 +3224,7 @@
         <v>95</v>
       </c>
       <c r="G50" t="n">
-        <v>0.00743107690211342</v>
+        <v>0.00741230379725906</v>
       </c>
       <c r="H50"/>
     </row>
@@ -3248,10 +3248,10 @@
         <v>142</v>
       </c>
       <c r="G51" t="n">
-        <v>0.00676741122361874</v>
+        <v>0.0067439889623678</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00285785858713188</v>
+        <v>0.00284210346859634</v>
       </c>
     </row>
     <row r="52">
@@ -3274,7 +3274,7 @@
         <v>64</v>
       </c>
       <c r="G52" t="n">
-        <v>0.00613877383033067</v>
+        <v>0.00612320169641204</v>
       </c>
       <c r="H52"/>
     </row>
@@ -3298,7 +3298,7 @@
         <v>146</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="H53"/>
     </row>
@@ -3322,7 +3322,7 @@
         <v>104</v>
       </c>
       <c r="G54" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="H54"/>
     </row>
@@ -3346,7 +3346,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="n">
-        <v>0.00387717660683835</v>
+        <v>0.00386730630254106</v>
       </c>
       <c r="H55"/>
     </row>
@@ -3370,7 +3370,7 @@
         <v>83</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00270225839922126</v>
+        <v>0.00269083255833109</v>
       </c>
       <c r="H56"/>
     </row>
@@ -3394,7 +3394,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00238499839618584</v>
+        <v>0.00238396688215094</v>
       </c>
       <c r="H57"/>
     </row>
@@ -3418,7 +3418,7 @@
         <v>92</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00161544568760096</v>
+        <v>0.00161141090867007</v>
       </c>
       <c r="H58"/>
     </row>
@@ -3442,7 +3442,7 @@
         <v>148</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0012924367675278</v>
+        <v>0.00128910210084702</v>
       </c>
       <c r="H59"/>
     </row>
@@ -3466,7 +3466,7 @@
         <v>31</v>
       </c>
       <c r="G60" t="n">
-        <v>0.000675564599805316</v>
+        <v>0.000672708139582772</v>
       </c>
       <c r="H60"/>
     </row>
@@ -3527,10 +3527,10 @@
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -3553,10 +3553,10 @@
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>16.5372588192262</v>
+        <v>16.5329845316454</v>
       </c>
       <c r="H3" t="n">
-        <v>3.04154912689679</v>
+        <v>3.04051963402742</v>
       </c>
     </row>
     <row r="4">
@@ -3579,10 +3579,10 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="5">
@@ -3605,10 +3605,10 @@
         <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>11.7230544408811</v>
+        <v>11.7236546644519</v>
       </c>
       <c r="H5" t="n">
-        <v>1.38906066577268</v>
+        <v>1.38912905347294</v>
       </c>
     </row>
     <row r="6">
@@ -3631,10 +3631,10 @@
         <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>10.0799264008542</v>
+        <v>10.0802443137262</v>
       </c>
       <c r="H6" t="n">
-        <v>0.497528984762263</v>
+        <v>0.497542723654256</v>
       </c>
     </row>
     <row r="7">
@@ -3657,10 +3657,10 @@
         <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="H7" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="8">
@@ -3683,10 +3683,10 @@
         <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>5.47371315766783</v>
+        <v>5.47426332536916</v>
       </c>
       <c r="H8" t="n">
-        <v>0.725016650401825</v>
+        <v>0.725104134642925</v>
       </c>
     </row>
     <row r="9">
@@ -3709,10 +3709,10 @@
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>3.76893878922744</v>
+        <v>3.76987050415154</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0636877863152674</v>
+        <v>0.0637147014776062</v>
       </c>
     </row>
     <row r="10">
@@ -3735,10 +3735,10 @@
         <v>34</v>
       </c>
       <c r="G10" t="n">
-        <v>2.35711416912975</v>
+        <v>2.35719235917727</v>
       </c>
       <c r="H10" t="n">
-        <v>0.204291718921909</v>
+        <v>0.204302288466635</v>
       </c>
     </row>
     <row r="11">
@@ -3761,10 +3761,10 @@
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="H11" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="12">
@@ -3787,10 +3787,10 @@
         <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>1.51390231586276</v>
+        <v>1.51398482750938</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0492796742344197</v>
+        <v>0.0492823020955965</v>
       </c>
     </row>
     <row r="13">
@@ -3813,10 +3813,10 @@
         <v>104</v>
       </c>
       <c r="G13" t="n">
-        <v>1.32056948721848</v>
+        <v>1.32060121834943</v>
       </c>
       <c r="H13" t="n">
-        <v>0.355227968619002</v>
+        <v>0.35523739701465</v>
       </c>
     </row>
     <row r="14">
@@ -3839,10 +3839,10 @@
         <v>30</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26562125220215</v>
+        <v>1.26569079615314</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0294564339085155</v>
+        <v>0.0294573793386389</v>
       </c>
     </row>
     <row r="15">
@@ -3865,10 +3865,10 @@
         <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="H15" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="16">
@@ -3891,10 +3891,10 @@
         <v>71</v>
       </c>
       <c r="G16" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="17">
@@ -3917,10 +3917,10 @@
         <v>138</v>
       </c>
       <c r="G17" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="H17" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="18">
@@ -3943,10 +3943,10 @@
         <v>73</v>
       </c>
       <c r="G18" t="n">
-        <v>0.592633978638086</v>
+        <v>0.592619268970162</v>
       </c>
       <c r="H18" t="n">
-        <v>0.213338796403032</v>
+        <v>0.213329511213247</v>
       </c>
     </row>
     <row r="19">
@@ -3969,10 +3969,10 @@
         <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>0.351175985734941</v>
+        <v>0.351322253471971</v>
       </c>
       <c r="H19" t="n">
-        <v>0.063645753435139</v>
+        <v>0.063670868567551</v>
       </c>
     </row>
     <row r="20">
@@ -3995,10 +3995,10 @@
         <v>31</v>
       </c>
       <c r="G20" t="n">
-        <v>0.334808283505506</v>
+        <v>0.334864889368922</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0213862302764069</v>
+        <v>0.0213890199646482</v>
       </c>
     </row>
     <row r="21">
@@ -4021,10 +4021,10 @@
         <v>91</v>
       </c>
       <c r="G21" t="n">
-        <v>0.315533179010191</v>
+        <v>0.315664450816511</v>
       </c>
       <c r="H21" t="n">
-        <v>0.137830515667426</v>
+        <v>0.137885777517319</v>
       </c>
     </row>
     <row r="22">
@@ -4047,10 +4047,10 @@
         <v>150</v>
       </c>
       <c r="G22" t="n">
-        <v>0.295145624389156</v>
+        <v>0.295190449716847</v>
       </c>
       <c r="H22" t="n">
-        <v>0.204404607400901</v>
+        <v>0.204437888414301</v>
       </c>
     </row>
     <row r="23">
@@ -4073,10 +4073,10 @@
         <v>76</v>
       </c>
       <c r="G23" t="n">
-        <v>0.242175367283282</v>
+        <v>0.242160708289927</v>
       </c>
       <c r="H23" t="n">
-        <v>0.105117748515762</v>
+        <v>0.105102080516384</v>
       </c>
     </row>
     <row r="24">
@@ -4099,7 +4099,7 @@
         <v>151</v>
       </c>
       <c r="G24" t="n">
-        <v>0.212351047265552</v>
+        <v>0.212345660707166</v>
       </c>
       <c r="H24"/>
     </row>
@@ -4123,10 +4123,10 @@
         <v>152</v>
       </c>
       <c r="G25" t="n">
-        <v>0.201693532470772</v>
+        <v>0.201728236934702</v>
       </c>
       <c r="H25" t="n">
-        <v>0.048108553541404</v>
+        <v>0.048105500208644</v>
       </c>
     </row>
     <row r="26">
@@ -4149,10 +4149,10 @@
         <v>101</v>
       </c>
       <c r="G26" t="n">
-        <v>0.15812321900899</v>
+        <v>0.158187424211174</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0798332359822568</v>
+        <v>0.0798625220540073</v>
       </c>
     </row>
     <row r="27">
@@ -4175,10 +4175,10 @@
         <v>69</v>
       </c>
       <c r="G27" t="n">
-        <v>0.146974458714768</v>
+        <v>0.146966996070451</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0129045399311217</v>
+        <v>0.0129042651403242</v>
       </c>
     </row>
     <row r="28">
@@ -4201,10 +4201,10 @@
         <v>97</v>
       </c>
       <c r="G28" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="29">
@@ -4227,10 +4227,10 @@
         <v>59</v>
       </c>
       <c r="G29" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="H29" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="30">
@@ -4253,7 +4253,7 @@
         <v>124</v>
       </c>
       <c r="G30" t="n">
-        <v>0.078814578864233</v>
+        <v>0.0788203573425972</v>
       </c>
       <c r="H30"/>
     </row>
@@ -4277,10 +4277,10 @@
         <v>126</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0767766031568904</v>
+        <v>0.0767885465735697</v>
       </c>
       <c r="H31" t="n">
-        <v>0.00674044272963043</v>
+        <v>0.0067414249958013</v>
       </c>
     </row>
     <row r="32">
@@ -4303,10 +4303,10 @@
         <v>100</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="33">
@@ -4329,7 +4329,7 @@
         <v>54</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0730903125241704</v>
+        <v>0.0730940892896911</v>
       </c>
       <c r="H33"/>
     </row>
@@ -4353,10 +4353,10 @@
         <v>133</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0669521263651332</v>
+        <v>0.0669679113379792</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00894656365606824</v>
+        <v>0.00894835440130837</v>
       </c>
     </row>
     <row r="35">
@@ -4379,10 +4379,10 @@
         <v>114</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0625501941406329</v>
+        <v>0.0625693354883635</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0067821560765687</v>
+        <v>0.00678591990212035</v>
       </c>
     </row>
     <row r="36">
@@ -4405,7 +4405,7 @@
         <v>142</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0621202460293485</v>
+        <v>0.0621248227529827</v>
       </c>
       <c r="H36"/>
     </row>
@@ -4429,10 +4429,10 @@
         <v>96</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0577451720243945</v>
+        <v>0.0577727984075593</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00615561606809399</v>
+        <v>0.00615693902785514</v>
       </c>
     </row>
     <row r="38">
@@ -4455,10 +4455,10 @@
         <v>92</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0495380365661187</v>
+        <v>0.0495498540995747</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00736556453700803</v>
+        <v>0.00736707645047622</v>
       </c>
     </row>
     <row r="39">
@@ -4481,10 +4481,10 @@
         <v>123</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0459537638479654</v>
+        <v>0.0459740490217306</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0094901820429826</v>
+        <v>0.00949304968572704</v>
       </c>
     </row>
     <row r="40">
@@ -4507,10 +4507,10 @@
         <v>103</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0439933304196353</v>
+        <v>0.043986841089278</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0261664828828586</v>
+        <v>0.0261566748666346</v>
       </c>
     </row>
     <row r="41">
@@ -4533,10 +4533,10 @@
         <v>58</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0367236334629408</v>
+        <v>0.0367300028822527</v>
       </c>
       <c r="H41" t="n">
-        <v>0.00554384650356856</v>
+        <v>0.00554647325349502</v>
       </c>
     </row>
     <row r="42">
@@ -4559,10 +4559,10 @@
         <v>108</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0365713646859972</v>
+        <v>0.0365853684413202</v>
       </c>
       <c r="H42" t="n">
-        <v>0.00787153471918318</v>
+        <v>0.0078751496126478</v>
       </c>
     </row>
     <row r="43">
@@ -4585,7 +4585,7 @@
         <v>146</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="H43"/>
     </row>
@@ -4609,7 +4609,7 @@
         <v>102</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0259313943733403</v>
+        <v>0.0259343842821128</v>
       </c>
       <c r="H44"/>
     </row>
@@ -4633,7 +4633,7 @@
         <v>153</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="H45"/>
     </row>
@@ -4657,7 +4657,7 @@
         <v>154</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0221796909801125</v>
+        <v>0.0221801678579688</v>
       </c>
       <c r="H46"/>
     </row>
@@ -4681,10 +4681,10 @@
         <v>140</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0204826413821713</v>
+        <v>0.0204865591798642</v>
       </c>
       <c r="H47" t="n">
-        <v>0.000426852181464751</v>
+        <v>0.000427153986817937</v>
       </c>
     </row>
     <row r="48">
@@ -4707,10 +4707,10 @@
         <v>87</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0163092206223587</v>
+        <v>0.0163086158082577</v>
       </c>
       <c r="H48" t="n">
-        <v>0.00700928958906865</v>
+        <v>0.00701053084458542</v>
       </c>
     </row>
     <row r="49">
@@ -4733,10 +4733,10 @@
         <v>85</v>
       </c>
       <c r="G49" t="n">
-        <v>0.015787218129565</v>
+        <v>0.0157889711102967</v>
       </c>
       <c r="H49" t="n">
-        <v>0.00588204337348365</v>
+        <v>0.00588424684009715</v>
       </c>
     </row>
     <row r="50">
@@ -4759,10 +4759,10 @@
         <v>129</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0157066434709264</v>
+        <v>0.0157129730732199</v>
       </c>
       <c r="H50" t="n">
-        <v>0.00644455578850006</v>
+        <v>0.00644786593254792</v>
       </c>
     </row>
     <row r="51">
@@ -4785,10 +4785,10 @@
         <v>128</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0118024547022103</v>
+        <v>0.0118043788700566</v>
       </c>
       <c r="H51" t="n">
-        <v>0.00691877303390335</v>
+        <v>0.00692066009538753</v>
       </c>
     </row>
     <row r="52">
@@ -4811,10 +4811,10 @@
         <v>119</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0115267247547719</v>
+        <v>0.0115291836987614</v>
       </c>
       <c r="H52" t="n">
-        <v>0.000846464203009839</v>
+        <v>0.000849967633715466</v>
       </c>
     </row>
     <row r="53">
@@ -4837,10 +4837,10 @@
         <v>116</v>
       </c>
       <c r="G53" t="n">
-        <v>0.00822078116659366</v>
+        <v>0.00822619208734681</v>
       </c>
       <c r="H53" t="n">
-        <v>0.000909803377331876</v>
+        <v>0.000910625346116799</v>
       </c>
     </row>
     <row r="54">
@@ -4863,7 +4863,7 @@
         <v>121</v>
       </c>
       <c r="G54" t="n">
-        <v>0.00742521471180896</v>
+        <v>0.00743308436708383</v>
       </c>
       <c r="H54"/>
     </row>
@@ -4887,10 +4887,10 @@
         <v>131</v>
       </c>
       <c r="G55" t="n">
-        <v>0.00654430843040156</v>
+        <v>0.00654449193357052</v>
       </c>
       <c r="H55" t="n">
-        <v>0.00215677517739025</v>
+        <v>0.00215414214857648</v>
       </c>
     </row>
     <row r="56">
@@ -4913,7 +4913,7 @@
         <v>155</v>
       </c>
       <c r="G56" t="n">
-        <v>0.00579574385982276</v>
+        <v>0.00579642008713082</v>
       </c>
       <c r="H56"/>
     </row>
@@ -4937,10 +4937,10 @@
         <v>95</v>
       </c>
       <c r="G57" t="n">
-        <v>0.00544138864064831</v>
+        <v>0.00544111302489999</v>
       </c>
       <c r="H57" t="n">
-        <v>0.00199442737963186</v>
+        <v>0.0019924666610927</v>
       </c>
     </row>
     <row r="58">
@@ -4963,7 +4963,7 @@
         <v>156</v>
       </c>
       <c r="G58" t="n">
-        <v>0.00305750505737567</v>
+        <v>0.0030607072709903</v>
       </c>
       <c r="H58"/>
     </row>
@@ -4987,7 +4987,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="n">
-        <v>0.00263188891698581</v>
+        <v>0.00263091780205172</v>
       </c>
       <c r="H59"/>
     </row>
@@ -5011,7 +5011,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="n">
-        <v>0.00263188891698581</v>
+        <v>0.00263091780205172</v>
       </c>
       <c r="H60"/>
     </row>
@@ -5035,7 +5035,7 @@
         <v>157</v>
       </c>
       <c r="G61" t="n">
-        <v>0.00252748841842708</v>
+        <v>0.00252893753007687</v>
       </c>
       <c r="H61"/>
     </row>
@@ -5059,7 +5059,7 @@
         <v>158</v>
       </c>
       <c r="G62" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="H62"/>
     </row>
@@ -5083,7 +5083,7 @@
         <v>159</v>
       </c>
       <c r="G63" t="n">
-        <v>0.00183588926511166</v>
+        <v>0.00183521185829894</v>
       </c>
       <c r="H63"/>
     </row>
@@ -5107,7 +5107,7 @@
         <v>160</v>
       </c>
       <c r="G64" t="n">
-        <v>0.00137691694883374</v>
+        <v>0.0013764088937242</v>
       </c>
       <c r="H64"/>
     </row>
@@ -5131,7 +5131,7 @@
         <v>107</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00131042119560235</v>
+        <v>0.00131166982510323</v>
       </c>
       <c r="H65"/>
     </row>
@@ -5155,7 +5155,7 @@
         <v>118</v>
       </c>
       <c r="G66" t="n">
-        <v>0.00119930614215706</v>
+        <v>0.00119886362192086</v>
       </c>
       <c r="H66"/>
     </row>
@@ -5179,7 +5179,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="n">
-        <v>0.000817876104891649</v>
+        <v>0.000818656917912728</v>
       </c>
       <c r="H67"/>
     </row>
